--- a/LinuxSDK/DTAPI/Doc/CapList.xlsx
+++ b/LinuxSDK/DTAPI/Doc/CapList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DekTecSCM_RELEASE\SW\CrossPlatform\SDK\DISTRI\WinSDK\DTAPI\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47C14186-158D-48AF-BA11-339EC920E92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A66E941-F707-4B6A-88E2-6706B13277BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12735" xr2:uid="{46B54BB2-037C-4E29-8198-681EB24EEB3C}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12735" xr2:uid="{86EEF246-1CF3-4CAA-A85F-444765072D83}"/>
   </bookViews>
   <sheets>
     <sheet name="IO Capabilities" sheetId="1" r:id="rId1"/>
@@ -2512,7 +2512,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B1BCE8C-AA75-4207-B004-95F48D856A69}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01804564-67B0-40E4-BA1E-D2F944B71726}">
   <dimension ref="A1:FR152"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6099,7 +6099,7 @@
       <c r="DU17" s="58"/>
       <c r="DV17" s="38"/>
       <c r="DW17" s="56"/>
-      <c r="DX17" s="56"/>
+      <c r="DX17" s="80"/>
       <c r="DY17" s="58"/>
       <c r="DZ17" s="38"/>
       <c r="EA17" s="56"/>
@@ -6116,10 +6116,10 @@
       <c r="EL17" s="58"/>
       <c r="EM17" s="38"/>
       <c r="EN17" s="56"/>
-      <c r="EO17" s="56"/>
+      <c r="EO17" s="80"/>
       <c r="EP17" s="56"/>
       <c r="EQ17" s="56"/>
-      <c r="ER17" s="56"/>
+      <c r="ER17" s="80"/>
       <c r="ES17" s="58"/>
       <c r="ET17" s="40"/>
       <c r="EU17" s="40"/>
@@ -7227,7 +7227,7 @@
       <c r="DU23" s="58"/>
       <c r="DV23" s="38"/>
       <c r="DW23" s="80"/>
-      <c r="DX23" s="80"/>
+      <c r="DX23" s="56"/>
       <c r="DY23" s="58"/>
       <c r="DZ23" s="38"/>
       <c r="EA23" s="56"/>
@@ -7244,10 +7244,10 @@
       <c r="EL23" s="58"/>
       <c r="EM23" s="38"/>
       <c r="EN23" s="80"/>
-      <c r="EO23" s="80"/>
+      <c r="EO23" s="56"/>
       <c r="EP23" s="56"/>
       <c r="EQ23" s="80"/>
-      <c r="ER23" s="80"/>
+      <c r="ER23" s="56"/>
       <c r="ES23" s="58"/>
       <c r="ET23" s="45"/>
       <c r="EU23" s="40"/>
@@ -30677,7 +30677,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9EE651-DF6F-42A0-98A9-5C10D2ED4A76}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470D3F36-264F-4079-9366-F7AF9DF305FD}">
   <dimension ref="A1:GB157"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -42395,7 +42395,7 @@
       <c r="CQ58" s="58"/>
       <c r="CR58" s="40"/>
       <c r="CS58" s="99"/>
-      <c r="CT58" s="104"/>
+      <c r="CT58" s="61"/>
       <c r="CU58" s="58"/>
       <c r="CV58" s="40"/>
       <c r="CW58" s="38"/>
@@ -61281,7 +61281,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{475BEAC6-2127-465C-AF49-06F6CE491650}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{033237DA-EEC7-4536-AA4B-78353E8309A6}">
   <dimension ref="A1:Y68"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -63794,7 +63794,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{492F5FBA-8263-4DC2-B1AB-E214048B8424}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5CBECBF-4AA8-47BD-B8AC-D8A3475AC583}">
   <dimension ref="A1:Z58"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>

--- a/LinuxSDK/DTAPI/Doc/CapList.xlsx
+++ b/LinuxSDK/DTAPI/Doc/CapList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DekTecSCM_RELEASE\SW\CrossPlatform\SDK\DISTRI\WinSDK\DTAPI\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A66E941-F707-4B6A-88E2-6706B13277BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{948F68C9-BF0A-416D-A056-6C21ABD72603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12735" xr2:uid="{86EEF246-1CF3-4CAA-A85F-444765072D83}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{0331753F-21D0-485C-8E64-78D81131D9B1}"/>
   </bookViews>
   <sheets>
     <sheet name="IO Capabilities" sheetId="1" r:id="rId1"/>
@@ -2512,7 +2512,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01804564-67B0-40E4-BA1E-D2F944B71726}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7332DD61-BB3A-40C3-9F1C-6C15FE8DD78D}">
   <dimension ref="A1:FR152"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -30677,7 +30677,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{470D3F36-264F-4079-9366-F7AF9DF305FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35FA85CC-55CD-4AB4-9B59-924254C3402C}">
   <dimension ref="A1:GB157"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -61281,7 +61281,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{033237DA-EEC7-4536-AA4B-78353E8309A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E67630A-CAB0-4F90-AB1E-EFAC577744AE}">
   <dimension ref="A1:Y68"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -63794,7 +63794,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5CBECBF-4AA8-47BD-B8AC-D8A3475AC583}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D43009-01BC-4DCE-9C36-0B539A3344C7}">
   <dimension ref="A1:Z58"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>

--- a/LinuxSDK/DTAPI/Doc/CapList.xlsx
+++ b/LinuxSDK/DTAPI/Doc/CapList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DekTecSCM_RELEASE\SW\CrossPlatform\SDK\DISTRI\WinSDK\DTAPI\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{948F68C9-BF0A-416D-A056-6C21ABD72603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23BC2F88-0000-4111-ACE3-620D2FD0044B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{0331753F-21D0-485C-8E64-78D81131D9B1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{7E498810-FD60-422C-9148-616EB580C79E}"/>
   </bookViews>
   <sheets>
     <sheet name="IO Capabilities" sheetId="1" r:id="rId1"/>
@@ -2512,7 +2512,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7332DD61-BB3A-40C3-9F1C-6C15FE8DD78D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B367E9E5-B26C-4CEA-A38A-1138DDA0F6C1}">
   <dimension ref="A1:FR152"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -30677,7 +30677,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35FA85CC-55CD-4AB4-9B59-924254C3402C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D7B2C8-C278-4F4B-9CAC-8BE6B0283AFF}">
   <dimension ref="A1:GB157"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -61281,7 +61281,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E67630A-CAB0-4F90-AB1E-EFAC577744AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3090D9F8-AD2A-444E-944B-F874B3C8BD52}">
   <dimension ref="A1:Y68"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -63794,7 +63794,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D43009-01BC-4DCE-9C36-0B539A3344C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{832D7A58-E809-45F9-B952-0BC98BB58444}">
   <dimension ref="A1:Z58"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>

--- a/LinuxSDK/DTAPI/Doc/CapList.xlsx
+++ b/LinuxSDK/DTAPI/Doc/CapList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DekTecSCM_RELEASE\SW\CrossPlatform\SDK\DISTRI\WinSDK\DTAPI\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23BC2F88-0000-4111-ACE3-620D2FD0044B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E79BB4B-0D21-4F95-9461-E830823175ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{7E498810-FD60-422C-9148-616EB580C79E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{556BD528-C5F7-4526-B786-12DEC267AAAA}"/>
   </bookViews>
   <sheets>
     <sheet name="IO Capabilities" sheetId="1" r:id="rId1"/>
@@ -2512,7 +2512,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B367E9E5-B26C-4CEA-A38A-1138DDA0F6C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E6BDACD-5A19-41D6-9E89-144A014A59CA}">
   <dimension ref="A1:FR152"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -30677,7 +30677,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D7B2C8-C278-4F4B-9CAC-8BE6B0283AFF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAAA6155-2517-4A60-AE83-E409BD2D278C}">
   <dimension ref="A1:GB157"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -34392,24 +34392,24 @@
       <c r="CT17" s="59"/>
       <c r="CU17" s="60"/>
       <c r="CV17" s="41"/>
-      <c r="CW17" s="59"/>
-      <c r="CX17" s="76"/>
-      <c r="CY17" s="76"/>
-      <c r="CZ17" s="76"/>
+      <c r="CW17" s="74"/>
+      <c r="CX17" s="83"/>
+      <c r="CY17" s="83"/>
+      <c r="CZ17" s="83"/>
       <c r="DA17" s="60"/>
-      <c r="DB17" s="59"/>
-      <c r="DC17" s="76"/>
-      <c r="DD17" s="76"/>
-      <c r="DE17" s="76"/>
+      <c r="DB17" s="74"/>
+      <c r="DC17" s="83"/>
+      <c r="DD17" s="83"/>
+      <c r="DE17" s="83"/>
       <c r="DF17" s="60"/>
-      <c r="DG17" s="59"/>
-      <c r="DH17" s="76"/>
-      <c r="DI17" s="76"/>
-      <c r="DJ17" s="76"/>
-      <c r="DK17" s="76"/>
-      <c r="DL17" s="76"/>
-      <c r="DM17" s="76"/>
-      <c r="DN17" s="60"/>
+      <c r="DG17" s="74"/>
+      <c r="DH17" s="83"/>
+      <c r="DI17" s="83"/>
+      <c r="DJ17" s="83"/>
+      <c r="DK17" s="83"/>
+      <c r="DL17" s="83"/>
+      <c r="DM17" s="83"/>
+      <c r="DN17" s="68"/>
       <c r="DO17" s="67"/>
       <c r="DP17" s="74"/>
       <c r="DQ17" s="83"/>
@@ -61281,7 +61281,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3090D9F8-AD2A-444E-944B-F874B3C8BD52}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5AFE9FC-544C-4DAE-8C5A-80EE399F5B2C}">
   <dimension ref="A1:Y68"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -63794,7 +63794,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{832D7A58-E809-45F9-B952-0BC98BB58444}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F44E8007-3AFC-4369-83B1-2BB763B8B770}">
   <dimension ref="A1:Z58"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>

--- a/LinuxSDK/DTAPI/Doc/CapList.xlsx
+++ b/LinuxSDK/DTAPI/Doc/CapList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DekTecSCM_RELEASE\SW\CrossPlatform\SDK\DISTRI\WinSDK\DTAPI\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E79BB4B-0D21-4F95-9461-E830823175ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDDF891A-343E-46E6-94E2-0FA978B70D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{556BD528-C5F7-4526-B786-12DEC267AAAA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{22A288F7-13B4-4CE5-850C-BD4DC5C4D2FA}"/>
   </bookViews>
   <sheets>
     <sheet name="IO Capabilities" sheetId="1" r:id="rId1"/>
@@ -2512,7 +2512,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E6BDACD-5A19-41D6-9E89-144A014A59CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB3EFFCF-0A96-4D4A-A3E7-CD23E93F25AB}">
   <dimension ref="A1:FR152"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -30677,7 +30677,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAAA6155-2517-4A60-AE83-E409BD2D278C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BCA493A-FF4F-4CA0-BDAB-3E7F990F4F22}">
   <dimension ref="A1:GB157"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -61281,7 +61281,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5AFE9FC-544C-4DAE-8C5A-80EE399F5B2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F40063B-01AF-4A00-89EB-E71B6F8D8CE6}">
   <dimension ref="A1:Y68"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -63794,7 +63794,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F44E8007-3AFC-4369-83B1-2BB763B8B770}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12C22BB8-D79B-43AF-93D9-D221BD41103C}">
   <dimension ref="A1:Z58"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>

--- a/LinuxSDK/DTAPI/Doc/CapList.xlsx
+++ b/LinuxSDK/DTAPI/Doc/CapList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DekTecSCM_RELEASE\SW\CrossPlatform\SDK\DISTRI\WinSDK\DTAPI\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDDF891A-343E-46E6-94E2-0FA978B70D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{24ABFC5A-BB27-4CED-923A-3F0DF8B554EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{22A288F7-13B4-4CE5-850C-BD4DC5C4D2FA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{907C3A62-0613-4BBE-9EDD-D76194E3B0B7}"/>
   </bookViews>
   <sheets>
     <sheet name="IO Capabilities" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -2512,7 +2515,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB3EFFCF-0A96-4D4A-A3E7-CD23E93F25AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7178D454-8EB5-40F3-848B-76D62B453587}">
   <dimension ref="A1:FR152"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -30677,7 +30680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BCA493A-FF4F-4CA0-BDAB-3E7F990F4F22}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33D2DE33-DC9D-4562-9843-504EF8122C62}">
   <dimension ref="A1:GB157"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -61281,7 +61284,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F40063B-01AF-4A00-89EB-E71B6F8D8CE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BADDBD74-A5ED-4C0B-93AE-F175EF4DFD33}">
   <dimension ref="A1:Y68"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -63794,7 +63797,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12C22BB8-D79B-43AF-93D9-D221BD41103C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E890A53E-97A9-4102-BF27-31D03F643341}">
   <dimension ref="A1:Z58"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
